--- a/POS_Lanes_TestData.xlsx
+++ b/POS_Lanes_TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BanuchandhiranM\Git\POS_Lanes_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E1617B-D4E0-4058-98CE-AF9631F3FA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DA005B-A158-42D0-A4BC-136D5A8E777A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="19190" windowHeight="11270" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="180">
   <si>
     <t>fileName</t>
   </si>
@@ -202,9 +202,6 @@
   </si>
   <si>
     <t>VfQueryUpdate.exe</t>
-  </si>
-  <si>
-    <t>PASS</t>
   </si>
   <si>
     <t xml:space="preserve">Diebold Nixdorf | Diebold Nixdorf Universal TouchDriver | 2.2.14 </t>
@@ -1378,7 +1375,7 @@
         <v>37</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -1647,10 +1644,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>131</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>132</v>
       </c>
       <c r="C1" s="23" t="s">
         <v>3</v>
@@ -1658,15 +1655,15 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" t="s">
         <v>133</v>
-      </c>
-      <c r="B2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B3" s="24">
         <v>45973.791666666664</v>
@@ -1674,74 +1671,74 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
         <v>136</v>
-      </c>
-      <c r="B4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1763,16 +1760,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="23" t="s">
         <v>128</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>129</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>3</v>
@@ -1780,43 +1777,43 @@
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>62</v>
-      </c>
-      <c r="B3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>64</v>
-      </c>
-      <c r="B4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C5" s="21">
         <v>3.22</v>
@@ -1824,186 +1821,186 @@
     </row>
     <row r="6" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>66</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>70</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>74</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>78</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="21" t="s">
         <v>82</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="21" t="s">
         <v>87</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>89</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>91</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>93</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>95</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C22" s="21">
         <v>2023</v>
@@ -2011,153 +2008,153 @@
     </row>
     <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="21" t="s">
         <v>98</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>100</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>103</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>106</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>109</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>111</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>114</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>116</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>118</v>
-      </c>
-      <c r="B35" t="s">
-        <v>148</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C36" s="21">
         <v>2</v>
@@ -2165,13 +2162,13 @@
     </row>
     <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>121</v>
-      </c>
-      <c r="B37" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2196,16 +2193,16 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="23" t="s">
         <v>128</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>129</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>3</v>
@@ -2215,38 +2212,35 @@
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>62</v>
-      </c>
-      <c r="B3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>64</v>
-      </c>
-      <c r="B4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/POS_Lanes_TestData.xlsx
+++ b/POS_Lanes_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BanuchandhiranM\Git\POS_Lanes_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DA005B-A158-42D0-A4BC-136D5A8E777A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B73C4E4-6936-434A-AEF1-6D0486E8C8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19190" windowHeight="11270" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19190" windowHeight="11270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -564,7 +564,7 @@
     <t xml:space="preserve">Microsoft | WSE 2.0 SP3 </t>
   </si>
   <si>
-    <t>Array("Grocery", "Cigarettes") </t>
+    <t>Array("Grocery","Cigarettes")</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1311,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="9">
-        <v>12211999</v>
+        <v>12251997</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">

--- a/POS_Lanes_TestData.xlsx
+++ b/POS_Lanes_TestData.xlsx
@@ -8,24 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BanuchandhiranM\Git\POS_Lanes_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B73C4E4-6936-434A-AEF1-6D0486E8C8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622FB61F-D8EC-410A-91B4-CF7C28C1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19190" windowHeight="11270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19190" windowHeight="11270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
     <sheet name="CashFlow" sheetId="3" r:id="rId2"/>
-    <sheet name="FileValidation" sheetId="5" r:id="rId3"/>
-    <sheet name="PatchValidation" sheetId="7" r:id="rId4"/>
-    <sheet name="Versions" sheetId="6" r:id="rId5"/>
-    <sheet name="VersionValidation" sheetId="4" r:id="rId6"/>
+    <sheet name="VersionValidation" sheetId="4" r:id="rId3"/>
+    <sheet name="FileValidation" sheetId="5" r:id="rId4"/>
+    <sheet name="PatchValidation" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="174">
   <si>
     <t>fileName</t>
   </si>
@@ -204,219 +203,9 @@
     <t>VfQueryUpdate.exe</t>
   </si>
   <si>
-    <t xml:space="preserve">Diebold Nixdorf | Diebold Nixdorf Universal TouchDriver | 2.2.14 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2.14 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBM | IBM BigFix Client | 11.0.1.104 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0.1.104 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBM | Endpoint Manager for Remote Control Target | 10.1.0.0022 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1.0.0022 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft POS for .NET 1.12 | 1.12.1296.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12.1296.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola, Inc | OPOS Driver for Symbol Scanners v3.31 | 3.31.0001 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31.0001 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seiko Epson Corporation | EPSON OPOS ADK | 3.4.0.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4.0.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honeywell International, Inc | Honeywell OPOS Suite | 1.14.1.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14.1.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VeriFone Verifone UnifiedDriverInstaller64 Build3 | 5.0.5.2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0.5.2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datalogic | Datalogic OPOS 1.14 Driver | 1.14.153 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14.153 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCR StoreLine WinPOS | 8.4.8.7608 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4.8.7608 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delhaize America | Connected Payments | 1.0.0.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0.0.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2015-2019 Redistributable (x64) | 14.29.30133.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.29.30133.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2015-2019 Redistributable (x86) | 14.29.30133.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCR | Retail Platform Software for Windows | 5.3.6.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3.6.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapid7, Inc. | Rapid7 Insight Agent | 4.0.9.38 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0.9.38 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rrtQ | rrtQ Remote Lane Refresh Tool | 24.12.1.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.12.1.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lakeside Software | Work Blaze | 10.11.0010 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.11.0010 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autolt Team | Autolt v3.3.14.2 | 3.3.14.2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3.14.2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eclipse Eclipse IDE for Java Developers | 4.4.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP | Unified Functional Testing | 2023 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Access Database Engine | 16.0.5044.1000 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0.5044.1000 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation Microsoft Visual C++ 2010 x64 Redistributable | 10.0.40219 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0.40219 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2010 x86 Redistributable | 10.0.40219 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2012 Redistributable (x64) | 11.0.60610.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0.60610.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2012 Redistributable (x86) | 11.0.60610.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2022 Redistributable (x86) | 14.36.32532.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.36.32532.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2022 Redistributable (x64) | 14.36.32532.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft .NET Framework 4.8 | 4.8.4115.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8.4115.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | .NetCore Desktop Runtime (x86) | 6.0.3.31024 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0.3.31024 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | .NetCore Desktop Runtime (x64) | 6.0.3.31024 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft | WSE 2.0 SP3 | 2.0.5050.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0.5050.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft | WSE 3.0 | 3.0.5305.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0.5305.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft | Script Debugger | 16.0.58.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0.58.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selenium | Accelerated and Continuous automation Intel-Engine | 2.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle Java 8 | Update 221 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Update 221 </t>
-  </si>
-  <si>
-    <t>Diebold Nixdorf Universal TouchDriver</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IBM BigFix Client</t>
-  </si>
-  <si>
-    <t>Endpoint Manager for Remote Control Target</t>
-  </si>
-  <si>
-    <t>Application</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpectedVersion </t>
-  </si>
-  <si>
     <t>Actual Version</t>
   </si>
   <si>
-    <t>IBM BigFix Client</t>
-  </si>
-  <si>
     <t xml:space="preserve">HotfixID </t>
   </si>
   <si>
@@ -462,116 +251,308 @@
     <t>KB5070248</t>
   </si>
   <si>
-    <t xml:space="preserve">Oracle Java 8 </t>
-  </si>
-  <si>
-    <t>Selenium</t>
-  </si>
-  <si>
-    <t>Microsoft | Script Debugger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft | WSE 3.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenico | Ingenico A5:A22USB Drivers 3.22 | 3.22 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP | Unified Functional Testing </t>
-  </si>
-  <si>
-    <t>Eclipse Eclipse IDE for Java Developers</t>
-  </si>
-  <si>
-    <t>Autolt Team | Autolt v3.3.14.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lakeside Software | Work Blaze </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rrtQ | rrtQ Remote Lane Refresh Tool </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapid7, Inc. | Rapid7 Insight Agent </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCR | Retail Platform Software for Windows </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2015-2019 Redistributable (x86) </t>
-  </si>
-  <si>
-    <t>Microsoft Corporation | Microsoft Visual C++ 2015-2019 Redistributable (x64)</t>
-  </si>
-  <si>
-    <t>Delhaize America | Connected Payments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCR StoreLine WinPOS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datalogic | Datalogic OPOS 1.14 Driver </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VeriFone Verifone UnifiedDriverInstaller64 Build3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honeywell International, Inc | Honeywell OPOS Suite </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seiko Epson Corporation | EPSON OPOS ADK </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola, Inc | OPOS Driver for Symbol Scanners v3.31 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft POS for .NET </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenico | Ingenico A5:A22USB Drivers </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Access Database Engine </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2010 x86 Redistributable </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2012 Redistributable  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation Microsoft Visual C++ 2010 x64 Redistributable </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2012 Redistributable (x86) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2022 Redistributable (x86) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | Microsoft Visual C++ 2022 Redistributable (x64) </t>
-  </si>
-  <si>
-    <t>Microsoft Corporation | Microsoft .NET Framework 4.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | .NetCore Desktop Runtime (x86) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corporation | .NetCore Desktop Runtime (x64) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft | WSE 2.0 SP3 </t>
-  </si>
-  <si>
     <t>Array("Grocery","Cigarettes")</t>
+  </si>
+  <si>
+    <t>Application details</t>
+  </si>
+  <si>
+    <t>Mapped Application name</t>
+  </si>
+  <si>
+    <t>Diebold Nixdorf | Diebold Nixdorf Universal TouchDriver | 2.2.14</t>
+  </si>
+  <si>
+    <t>Diebold Nixdorf Universal TouchDriver|2.2.14</t>
+  </si>
+  <si>
+    <t>IBM | IBM BigFix Client | 11.0.1.104</t>
+  </si>
+  <si>
+    <t>BigFix Client|11.0.1.104</t>
+  </si>
+  <si>
+    <t>IBM | Endpoint Manager for Remote Control Target | 10.1.0.0022</t>
+  </si>
+  <si>
+    <t>BigFix Remote Control - Target|10.1.0.0022</t>
+  </si>
+  <si>
+    <t>Ingenico | Ingenico USB Drivers 3.22 | 3.22</t>
+  </si>
+  <si>
+    <t>Ingenico USB Drivers 3.22 (remove only)|3.22</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | Microsoft POS for .NET 1.12 | 1.12.1296.00</t>
+  </si>
+  <si>
+    <t>Microsoft POS for .NET 1.12|1.12.1296.00</t>
+  </si>
+  <si>
+    <t>Motorola, Inc | OPOS Driver for Symbol Scanners v3.31 | 3.31.0001</t>
+  </si>
+  <si>
+    <t>OPOS Driver for Symbol Scanners v3.31|3.31.0001</t>
+  </si>
+  <si>
+    <t>Seiko Epson Corporation | EPSON OPOS ADK | 3.4.0.0</t>
+  </si>
+  <si>
+    <t>EPSON OPOS ADK Ver3.00|3.4.0.0</t>
+  </si>
+  <si>
+    <t>Honeywell International, Inc | Honeywell OPOS Suite | 1.14.1.1</t>
+  </si>
+  <si>
+    <t>Honeywell OPOS Suite|1.14.1.1</t>
+  </si>
+  <si>
+    <t>VeriFone | VerifoneUnifiedDriverInstaller64 Build3 | 5.0.5.2</t>
+  </si>
+  <si>
+    <t>VerifoneUnifiedDriverInstaller64 Build 3|5.0.5.2</t>
+  </si>
+  <si>
+    <t>Datalogic | Datalogic OPOS 1.14 Driver | 1.14.153</t>
+  </si>
+  <si>
+    <t>Datalogic OPOS 1.14 Driver|1.14.153</t>
+  </si>
+  <si>
+    <t>NCR | StoreLine WinPOS | 8.4.8.7608</t>
+  </si>
+  <si>
+    <t>StoreLine WinPOS|8.4.8.7608</t>
+  </si>
+  <si>
+    <t>Delhaize America | Connected Payments | 1.0.0.0</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | Microsoft Visual C++ 2015-2019 Redistributable (x64) | 14.29.30133.0</t>
+  </si>
+  <si>
+    <t>Microsoft Visual C++ 2015-2022 Redistributable (x64) - 14.29.30133|14.29.30133.0</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | Microsoft Visual C++ 2015-2019 Redistributable (x86) | 14.29.30133.0</t>
+  </si>
+  <si>
+    <t>Microsoft Visual C++ 2015-2022 Redistributable (x86) - 14.29.30133|14.29.30133.0</t>
+  </si>
+  <si>
+    <t>NCR | Retail Platform Software for Windows | 5.3.6.0</t>
+  </si>
+  <si>
+    <t>Retail Platform Software for Windows|5.3.6.0</t>
+  </si>
+  <si>
+    <t>Rapid7, Inc. | Rapid7 Insight Agent | 4.0.9.38</t>
+  </si>
+  <si>
+    <t>Rapid7 Insight Agent|4.0.9.38</t>
+  </si>
+  <si>
+    <t>rrtQ | rrtQ Remote Lane Refresh Tool | 24.12.1.1</t>
+  </si>
+  <si>
+    <t>rrtQ Remote Lane Refresh Service|24.12.1.1</t>
+  </si>
+  <si>
+    <t>Lakeside Software | Work Blaze | 10.11.0010</t>
+  </si>
+  <si>
+    <t>Systems Management Agent|10.11.0010</t>
+  </si>
+  <si>
+    <t>AutoIt Team | AutoIt v3.3.14.2 | 3.3.14.2</t>
+  </si>
+  <si>
+    <t>AutoIt v3.3.14.2|3.3.14.2</t>
+  </si>
+  <si>
+    <t>Eclipse | Eclipse IDE for Java Developers | 4.4.1</t>
+  </si>
+  <si>
+    <t>Eclipse IDE for Java Developers|4.4.1</t>
+  </si>
+  <si>
+    <t>HP | Unified Functional Testing | 2023</t>
+  </si>
+  <si>
+    <t>Microsoft | Access Database Engine | 16.0.5044.1000</t>
+  </si>
+  <si>
+    <t>Microsoft Access database engine 2016 (English)|16.0.5044.1000</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | Microsoft Visual C++ 2010 x64 Redistributable | 10.0.40219</t>
+  </si>
+  <si>
+    <t>Microsoft Visual C++ 2010  x64 Redistributable - 10.0.40219|10.0.40219</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | Microsoft Visual C++ 2010 x86 Redistributable | 10.0.40219</t>
+  </si>
+  <si>
+    <t>Microsoft Visual C++ 2010  x86 Redistributable - 10.0.40219|10.0.40219</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | Microsoft Visual C++ 2012 Redistributable (x64) | 11.0.60610.1</t>
+  </si>
+  <si>
+    <t>Microsoft Visual C++ 2012 Redistributable (x64) - 11.0.60610|11.0.60610.1</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | Microsoft Visual C++ 2012 Redistributable (x86) | 11.0.60610.1</t>
+  </si>
+  <si>
+    <t>Microsoft Visual C++ 2012 Redistributable (x86) - 11.0.60610|11.0.60610.1</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | Microsoft Visual C++ 2022 Redistributable (x86) | 14.36.32532.0</t>
+  </si>
+  <si>
+    <t>Microsoft Visual C++ 2015-2022 Redistributable (x86) - 14.36.32532|14.36.32532.0</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | Microsoft Visual C++ 2022 Redistributable (x64) | 14.36.32532.0</t>
+  </si>
+  <si>
+    <t>Microsoft Visual C++ 2015-2022 Redistributable (x64) - 14.36.32532|14.36.32532.0</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | Microsoft .NET Framework 4.8 | 4.8.4115.0</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | .NetCore Desktop Runtime (x86) | 6.0.3.31024</t>
+  </si>
+  <si>
+    <t>Microsoft Windows Desktop Runtime - 6.0.3 (x86)|6.0.3.31024</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation | .NetCore Desktop Runtime (x64) | 6.0.3.31024</t>
+  </si>
+  <si>
+    <t>Microsoft Windows Desktop Runtime - 6.0.3 (x64)|6.0.3.31024</t>
+  </si>
+  <si>
+    <t>Microsoft | WSE 2.0 SP3 | 2.0.5050.0</t>
+  </si>
+  <si>
+    <t>Microsoft WSE 2.0 SP3 Runtime|2.0.5050.0</t>
+  </si>
+  <si>
+    <t>Microsoft | WSE 3.0 | 3.0.5305.0</t>
+  </si>
+  <si>
+    <t>Microsoft WSE 3.0 Runtime|3.0.5305.0</t>
+  </si>
+  <si>
+    <t>Microsoft | Script Debugger | 16.0.58.0</t>
+  </si>
+  <si>
+    <t>VS Script Debugging Common|16.0.58.0</t>
+  </si>
+  <si>
+    <t>Selenium | Accelerated and Continuous automation Intel-Engine | 2.0</t>
+  </si>
+  <si>
+    <t>Accelerated and Continuous Automation Intel-Engine|2.0</t>
+  </si>
+  <si>
+    <t>Oracle | Java 8 | Update 221</t>
+  </si>
+  <si>
+    <t>Java 8 Update 221|8</t>
+  </si>
+  <si>
+    <t>2.2.14</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>NOT FOUND</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>11.0.1.104</t>
+  </si>
+  <si>
+    <t>10.1.0.0022</t>
+  </si>
+  <si>
+    <t>1.12.1296.00</t>
+  </si>
+  <si>
+    <t>3.31.0001</t>
+  </si>
+  <si>
+    <t>3.4.0.0</t>
+  </si>
+  <si>
+    <t>1.14.1.1</t>
+  </si>
+  <si>
+    <t>5.0.5.2</t>
+  </si>
+  <si>
+    <t>1.14.153</t>
+  </si>
+  <si>
+    <t>14.36.32532.0</t>
+  </si>
+  <si>
+    <t>5.3.6.0</t>
+  </si>
+  <si>
+    <t>4.1.1.55</t>
+  </si>
+  <si>
+    <t>25.1.1.0</t>
+  </si>
+  <si>
+    <t>10.11.0010</t>
+  </si>
+  <si>
+    <t>3.3.14.2</t>
+  </si>
+  <si>
+    <t>4.4.1</t>
+  </si>
+  <si>
+    <t>16.0.5044.1000</t>
+  </si>
+  <si>
+    <t>10.0.40219</t>
+  </si>
+  <si>
+    <t>11.0.60610.1</t>
+  </si>
+  <si>
+    <t>6.0.3.31024</t>
+  </si>
+  <si>
+    <t>2.0.5050.0</t>
+  </si>
+  <si>
+    <t>3.0.5305.0</t>
+  </si>
+  <si>
+    <t>16.0.58.0</t>
+  </si>
+  <si>
+    <t>8.0.2210.11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -621,25 +602,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -649,7 +611,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -755,27 +717,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFC4C7C5"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -815,21 +762,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1375,7 +1307,7 @@
         <v>37</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1384,6 +1316,543 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057ABCD7-B033-471E-982A-F548916DEC0D}">
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="79.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5">
+        <v>3.22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>168</v>
+      </c>
+      <c r="D26" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" t="s">
+        <v>169</v>
+      </c>
+      <c r="D32" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>137</v>
+      </c>
+      <c r="B33" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>139</v>
+      </c>
+      <c r="B34" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" t="s">
+        <v>171</v>
+      </c>
+      <c r="D34" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>141</v>
+      </c>
+      <c r="B35" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" t="s">
+        <v>172</v>
+      </c>
+      <c r="D35" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" t="s">
+        <v>173</v>
+      </c>
+      <c r="D37" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7194E4C6-8F65-4FE7-B439-C896D8BB88F2}">
   <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="44" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1633,7 +2102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF7291DC-D280-4A58-A7AB-484F822377A3}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1643,604 +2112,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="C1" s="23" t="s">
+      <c r="A1" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="24">
+        <v>64</v>
+      </c>
+      <c r="B3" s="19">
         <v>45973.791666666664</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7756EA94-73BC-42D8-B20B-FE18684BA22D}">
-  <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultColWidth="62.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="61.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.90625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="19" t="s">
         <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="21">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="C22" s="21">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" t="s">
-        <v>147</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B36" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" s="21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="B37" t="s">
-        <v>145</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>121</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057ABCD7-B033-471E-982A-F548916DEC0D}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="58.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
